--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-10-2025.xlsx
@@ -539,17 +539,17 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Regular price
-                  £10.35</t>
+                  £10.30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.17</t>
+          <t>£10.30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.17</t>
+          <t>£10.30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -661,17 +661,17 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Regular price
-                  £11.65</t>
+                  £11.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£13.30</t>
+          <t>£11.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£13.30</t>
+          <t>£11.60</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -783,17 +783,17 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.10</t>
+                  £15.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.95</t>
+          <t>£15.05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.95</t>
+          <t>£15.05</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -905,17 +905,17 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.40</t>
+                  £15.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.95</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.95</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1027,17 +1027,17 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Regular price
-                  £19.60</t>
+                  £19.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.50</t>
+          <t>£19.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.50</t>
+          <t>£19.52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1149,17 +1149,17 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.35</t>
+                  £21.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.95</t>
+          <t>£21.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.95</t>
+          <t>£21.30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.55</t>
+                  £21.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>£21.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>£21.53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.95</t>
+          <t>£24.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1515,17 +1515,17 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.80</t>
+                  £26.70</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.70</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.70</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.20</t>
+                  £26.40</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.95</t>
+          <t>£26.40</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1759,17 +1759,17 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Regular price
-                  £35.13</t>
+                  £35.10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£37.95</t>
+          <t>£35.10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£37.95</t>
+          <t>£35.10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1881,17 +1881,17 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Regular price
-                  £32.35</t>
+                  £32.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£32.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.95</t>
+          <t>£32.25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2003,17 +2003,17 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>Regular price
-                  £39.76</t>
+                  £39.70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£39.70</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£39.70</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£39.76</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£44.95</t>
+          <t>£39.99</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£44.95</t>
+          <t>£39.99</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£729.95</t>
+          <t>£695.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£729.95</t>
+          <t>£695.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£935.40</t>
+          <t>£895.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£935.40</t>
+          <t>£895.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6c9831eb5+80197]
-	GetHandleVerifier [0x0x7ff6c9831f10+80288]
-	(No symbol) [0x0x7ff6c95b02fa]
-	(No symbol) [0x0x7ff6c9607cd7]
-	(No symbol) [0x0x7ff6c9607f9c]
-	(No symbol) [0x0x7ff6c965ba87]
-	(No symbol) [0x0x7ff6c96303bf]
-	(No symbol) [0x0x7ff6c96587fb]
-	(No symbol) [0x0x7ff6c9630153]
-	(No symbol) [0x0x7ff6c95f8b02]
-	(No symbol) [0x0x7ff6c95f98d3]
-	GetHandleVerifier [0x0x7ff6c9aee83d+2949837]
-	GetHandleVerifier [0x0x7ff6c9ae8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6c9b086c7+3055959]
-	GetHandleVerifier [0x0x7ff6c984cfee+191102]
-	GetHandleVerifier [0x0x7ff6c98550af+224063]
-	GetHandleVerifier [0x0x7ff6c983af64+117236]
-	GetHandleVerifier [0x0x7ff6c983b119+117673]
-	GetHandleVerifier [0x0x7ff6c98210a8+11064]
+	GetHandleVerifier [0x0x7ff6042f1eb5+80197]
+	GetHandleVerifier [0x0x7ff6042f1f10+80288]
+	(No symbol) [0x0x7ff6040702fa]
+	(No symbol) [0x0x7ff6040c7cd7]
+	(No symbol) [0x0x7ff6040c7f9c]
+	(No symbol) [0x0x7ff60411ba87]
+	(No symbol) [0x0x7ff6040f03bf]
+	(No symbol) [0x0x7ff6041187fb]
+	(No symbol) [0x0x7ff6040f0153]
+	(No symbol) [0x0x7ff6040b8b02]
+	(No symbol) [0x0x7ff6040b98d3]
+	GetHandleVerifier [0x0x7ff6045ae83d+2949837]
+	GetHandleVerifier [0x0x7ff6045a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff6045c86c7+3055959]
+	GetHandleVerifier [0x0x7ff60430cfee+191102]
+	GetHandleVerifier [0x0x7ff6043150af+224063]
+	GetHandleVerifier [0x0x7ff6042faf64+117236]
+	GetHandleVerifier [0x0x7ff6042fb119+117673]
+	GetHandleVerifier [0x0x7ff6042e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
